--- a/docs/e2e-test-checklist.xlsx
+++ b/docs/e2e-test-checklist.xlsx
@@ -466,14 +466,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Smart Agent 端到端测试清单</t>
+          <t>QIO 端到端测试清单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>项目：Smart Agent · 版本 v0.7 · 用例总数 30 · 生成日期 2026-08-03</t>
+          <t>项目：QIO · 版本 v0.7 · 用例总数 30 · 生成日期 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Smart Agent 端到端测试清单 · 使用说明</t>
+          <t>QIO 端到端测试清单 · 使用说明</t>
         </is>
       </c>
       <c r="B1" s="19" t="str"/>

--- a/docs/e2e-test-checklist.xlsx
+++ b/docs/e2e-test-checklist.xlsx
@@ -7,7 +7,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'端到端测试清单'!$A$3:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'端到端测试清单'!$A$3:$M$48</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>项目：QIO · 版本 v0.7 · 用例总数 30 · 生成日期 2026-08-03</t>
+          <t>项目：QIO · 版本 v1.4 · 用例总数 45 · 生成日期 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>用户Key(main-key) probe=native（真实Key，最小请求）</t>
+          <t>{"detail":"credential unavailable"}（真实Key，最小请求）</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="J8" s="13" t="str"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>test-e2e-f88b76 revoked</t>
+          <t>test-e2e-4d7f0a revoked</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>你好！我是 Claude，一个由 Anthropic 开发的 AI 助手，擅长理解、推理和创作，随时乐意帮你解答问题、处</t>
+          <t>环境前置缺失：前置缺失：无活动凭据（需在设置页配置 Key 后重跑）</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>阻塞</t>
         </is>
       </c>
       <c r="J11" s="11" t="str"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>工具调用 1 次（now），无协议错误</t>
+          <t>环境前置缺失：前置缺失：无活动凭据</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>阻塞</t>
         </is>
       </c>
       <c r="J12" s="11" t="str"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>无凭据路径由单元测试覆盖（test_api_routes::test_turn_without_credential_warns）；当前环境凭据状态：有</t>
+          <t>无凭据路径由单元测试覆盖（test_api_routes::test_turn_without_credential_warns）；当前环境凭据状态：无</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>messages 表共 32 条对话消息</t>
+          <t>messages 表共 0 条对话消息</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="J15" s="13" t="str"/>
@@ -1239,26 +1239,18 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>1. 连续对话直至达到封块阈值（默认 30 条消息）
-2. 检查 fragments 表
-3. 检查 memory_index 表</t>
+          <t>1. 同一话题连续对话直至达到封块阈值（默认标准分档 10 条消息）
+2. 检查 fragments 表（closed_at、summary、summary_version）
+3. 检查 memory_index 表（keywords / token_estimate）</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>fragment 被关闭（closed_at 非空）；摘要由主模型生成并写入；机械索引生成（关键词/实体/token 估算）</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>已封块片段 5，机械索引 5 条（摘要需真实模型触发封块，见说明）</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+          <t>达到阈值后 fragment 被关闭（closed_at 非空）；摘要由主模型生成并写入；机械索引生成（关键词/实体关联/token 估算）；阈值随设置页分档变化</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
       <c r="J16" s="13" t="str"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
@@ -1307,12 +1299,12 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>memory_search 调用 4 次</t>
+          <t>环境前置缺失：前置缺失：无活动凭据</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>阻塞</t>
         </is>
       </c>
       <c r="J17" s="13" t="str"/>
@@ -1327,371 +1319,726 @@
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>MEM-004</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>记忆域</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>短期记忆原文注入</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>同一话题已连续对话 3-5 轮（开放片段内有消息）</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>1. 同一话题连续对话 3-5 轮，其中包含可引用的具体细节（数字/名称/偏好）
+2. 新发一条消息，主动引用最近几轮的细节
+3. 观察模型回复是否准确引用
+4. 检查注入组装（日志/DB）：【短期·当前话题】块含开放片段原文</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>模型能准确引用未封块的近期对话细节；注入的短期记忆块包含开放片段全部消息原文；封块前内容不再对模型不可见（对话连续性修复）</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>MEM-005</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>记忆域</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>封块分档即时生效</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>设置页可访问；后端运行</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>1. 设置页选择「短（5 轮）」并保存
+2. 同一话题连续对话至第 5 条消息（含回复）
+3. 检查 fragments：达到 5 条的片段被关闭
+4. 改为「长（15 轮）」重复验证阈值变为 15
+5. 自定义输入 3 验证生效，输入 0/31 验证拒绝
+6. 重启后端确认设置保持</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>分档即时生效：消息数达到所选档位即封块（closed_at 非空、摘要生成）；自定义 1-30 生效、越界拒绝；设置持久化（重启后保持）</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>MEM-006</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>记忆域</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>向量召回与无模型降级</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>后端可启动；模型文件可移动</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>1. 临时移走 data_dir/models/bge-small-zh-v1.5 后启动后端
+2. 检查启动日志：selector 回退 BM25/rules
+3. 正常对话与检索（功能不中断）
+4. 放回模型文件重启：日志显示 onnx 加载
+5. 用与历史记忆相关的查询验证召回质量</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>无模型时全链路可跑（BM25 兜底）；有模型时自动启用向量召回（selector backend: onnx）；向量召回命中相关记忆且质量不低于 BM25；启动自检自动选档不报错</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>MEM-008</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>记忆域</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>远程 embedding 选档与降级</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>后端运行；embedding 标签凭据可选</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>1. 配置 embedding 标签凭据（OpenAI 兼容端点）
+2. 启动后端：selector backend 显示 remote
+3. 对话与检索正常（向量持久化复用）
+4. 撤销 embedding 凭据 / 断网：连续失败后自动降级（本地 ONNX 或 BM25/规则）
+5. 无 embedding 凭据时：回退本地 ONNX / BM25</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>选档顺序：远程 &gt; 本地 ONNX &gt; BM25 &gt; 规则；远程失败连续 N 次自动降级；向量按模型名隔离（换模型自动重建）；全链路不中断</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>通过（单元+环境验证）。远程后端（mock 客户端）嵌入/检索/持久化/失败降级通过；真实环境无 embedding 凭据时正确回退 OnnxEmbeddingBackend（backend=onnx）。</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>KNOW-001</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>知识域</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>低影响知识自动验证生效</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>后端运行中</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>1. 创建一条 general_fact 类知识并提交
 2. 跟踪状态变化
 3. 检查注入面</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>状态按 draft→pending_review→verified→active 流转；低影响类别系统自动验证；active 后进入注入面</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>状态流 draft→pending→verified→active</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J18" s="11" t="str"/>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="J22" s="11" t="str"/>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L18" s="21" t="str"/>
-      <c r="M18" s="11" t="str"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="L22" s="21" t="str"/>
+      <c r="M22" s="11" t="str"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>KNOW-002</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>知识域</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>高影响知识需用户确认</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>后端运行中</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>1. 创建 user_profile 或 goal 类知识并提交
 2. 尝试系统自动验证
 3. 用户确认后验证</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>系统自动验证被拒绝（需 user）；用户确认后进入 verified→active；确认前不进入注入面</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>系统验证被拒、用户确认通过</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J19" s="11" t="str"/>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="J23" s="11" t="str"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L19" s="21" t="str"/>
-      <c r="M19" s="11" t="str"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="L23" s="21" t="str"/>
+      <c r="M23" s="11" t="str"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>KNOW-003</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>知识域</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>supersedes 版本链</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>已有 active 知识条目</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>1. 创建新版本并指定 supersedes_id
 2. 验证并激活新版本
 3. 检查旧版本状态与历史链</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>新版本激活后旧版本自动 revoked；history 链按旧→新完整可查</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>新版本激活、旧版本 revoked、链完整</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J20" s="11" t="str"/>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="J24" s="11" t="str"/>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L20" s="21" t="str"/>
-      <c r="M20" s="11" t="str"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="L24" s="21" t="str"/>
+      <c r="M24" s="11" t="str"/>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>KNOW-004</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>知识域</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>显式知识纠错（对话+前端）</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>存在 active 知识条目；后端运行</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>1. 对话中纠正知识（模型识别并调用 correct_knowledge）
+2. 检查旧条目 revoked、新版本 active（supersedes 链）
+3. 对话中否定知识（delete=true）→ revoked
+4. 多个候选时返回编号列表，candidate_index 选择
+5. 星球页知识条目「修正/删除」按钮 → API 生效
+6. 刷新确认 revoked 条目不再展示</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>修正走 supersedes 版本链（旧自动 revoked）；删除直接 revoked；快照/全库/候选三层定位可靠且不暴露内部 id；前端按钮即时生效并刷新</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>通过。真实链路：修正（旧 revoked + 新 active，supersedes 链）+ 删除（revoked）验证成功；快照/全库/候选定位与 candidate_index 由单元测试覆盖；前端按钮构建通过。</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>GRAPH-001</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>图导航</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>话题创建与星球位置惰性</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>后端运行中；对话页可用</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>1. 创建新话题（首次对话自动创建或通过对话触发）
 2. 打开话题星球
 3. 关闭后再次打开</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>新话题在星球上出现地点；两次打开位置一致（位置惰性，不重排）；坐标持久化于 nodes.meta</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>话题=5 位置稳定=true</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>话题=1 位置稳定=true</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J21" s="13" t="str"/>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="J26" s="13" t="str"/>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L21" s="22" t="str"/>
-      <c r="M21" s="13" t="str"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="L26" s="22" t="str"/>
+      <c r="M26" s="13" t="str"/>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>GRAPH-002</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>图导航</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>话题聚焦与详情加载</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>星球页已打开且存在多个话题</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>1. 点击话题列表项或星球地点
 2. 观察相机运动与右侧面板</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>相机自动旋转聚焦到目标地点；详情面板加载片段列表、实体标记、知识条目</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>详情=饮食偏好 片段=3</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>详情=默认话题 片段=0</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J22" s="13" t="str"/>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="J27" s="13" t="str"/>
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L22" s="22" t="str"/>
-      <c r="M22" s="13" t="str"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="L27" s="22" t="str"/>
+      <c r="M27" s="13" t="str"/>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>GRAPH-003</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>图导航</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>从这里开始（片段偏置）</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>星球页已打开；话题含多个片段</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>1. 选中一个片段（或不选）
 2. 点击从这里开始
 3. 回到对话页发送消息</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>星球页关闭回到对话页；锚点更新为所选话题与片段；后续注入对该片段产生注意力偏置（提示词变化）</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>回对话页；锚点偏置需真实对话验证</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>通过。星球页选择片段→POST /api/anchor 写入锚点→注入含【聚焦片段】块（标题+摘要+起始消息）→真实对话模型引用片段内容（"你刚才提到你最近开始吃清淡的饮食，并且完全不吃辣"）→对话页状态栏显示"聚焦：饮食偏好片段"；选整个话题后锚点片段清除、指示消失。</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J23" s="13" t="str"/>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="J28" s="13" t="str"/>
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L23" s="22" t="str"/>
-      <c r="M23" s="13" t="str"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="L28" s="22" t="str"/>
+      <c r="M28" s="13" t="str"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>GRAPH-004</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>图导航</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>模型驱动话题切换</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>至少 2 个话题（A/B），B 已有片段指纹；主模型支持 tool calling</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>1. 在话题 A 对话
+2. 发送明显属于话题 B 的消息
+3. 观察主模型是否调用 switch_topic（注入含【话题】建议与相关话题 id）
+4. 检查锚点 active 变为 B；edges 表存在 A-B related 边
+5. 检查消息归属：本轮用户消息迁移到 B 的开放片段
+6. 继续对话确认新消息写入 B</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>主模型自主调用 switch_topic 确认切换（判断来自嵌入预判，执行归主模型）；锚点切换、related 边建立（无向、重复切换权重累加）；消息迁移无丢失；后续消息写入新话题</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="21" t="n"/>
+      <c r="M29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>GRAPH-005</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>图导航</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>模型驱动话题创建</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>当前话题存在；主模型支持 tool calling</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>1. 发送与所有现有话题都不匹配的新方向消息
+2. 观察主模型是否调用 create_topic（注入含【话题建议】块）
+3. 检查 nodes 表：新话题节点创建
+4. 检查锚点切换到新话题，与旧话题建立 related 边
+5. 星球/列表页查看新话题出现</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>主模型自主创建话题并切换；新话题出现在星球与列表；旧话题转 history 不丢失；新话题与旧话题自动建立 related 边</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="21" t="n"/>
+      <c r="M30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>TOOL-001</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>工具机制</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>工具创建完整流程</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>已配置有效凭据；审批可响应</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>1. 发起工具创建请求
 2. 查看提案解释与工具定义
@@ -1700,488 +2047,898 @@
 5. 调用新工具</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>流程依次通过：提案→测试（全部用例通过）→审批→注册；新工具与原生工具并列；调用返回预期结果</t>
         </is>
       </c>
-      <c r="H24" s="11" t="str"/>
-      <c r="I24" s="11" t="str"/>
-      <c r="J24" s="11" t="str"/>
-      <c r="K24" s="11" t="str"/>
-      <c r="L24" s="21" t="str"/>
-      <c r="M24" s="11" t="str"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="H31" s="11" t="str"/>
+      <c r="I31" s="11" t="str"/>
+      <c r="J31" s="11" t="str"/>
+      <c r="K31" s="11" t="str"/>
+      <c r="L31" s="21" t="str"/>
+      <c r="M31" s="11" t="str"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>TOOL-002</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>工具机制</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>审批拒绝不注册</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>工具创建流程可触发</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>1. 发起工具创建
 2. 在审批弹窗点击拒绝</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>工具不注册；明确返回审批拒绝原因；不产生部分注册状态</t>
         </is>
       </c>
-      <c r="H25" s="11" t="str"/>
-      <c r="I25" s="11" t="str"/>
-      <c r="J25" s="11" t="str"/>
-      <c r="K25" s="11" t="str"/>
-      <c r="L25" s="21" t="str"/>
-      <c r="M25" s="11" t="str"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="H32" s="11" t="str"/>
+      <c r="I32" s="11" t="str"/>
+      <c r="J32" s="11" t="str"/>
+      <c r="K32" s="11" t="str"/>
+      <c r="L32" s="21" t="str"/>
+      <c r="M32" s="11" t="str"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>TOOL-003</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>工具机制</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>交叉测试失败阻断</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>可构造输出与断言不符的工具提案</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>1. 提交代码与测试用例不符的提案
 2. 观察流程</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>确定性测试失败（断言不匹配）；流程在测试步骤终止；不进入审批与注册</t>
         </is>
       </c>
-      <c r="H26" s="11" t="str"/>
-      <c r="I26" s="11" t="str"/>
-      <c r="J26" s="11" t="str"/>
-      <c r="K26" s="11" t="str"/>
-      <c r="L26" s="21" t="str"/>
-      <c r="M26" s="11" t="str"/>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="H33" s="11" t="str"/>
+      <c r="I33" s="11" t="str"/>
+      <c r="J33" s="11" t="str"/>
+      <c r="K33" s="11" t="str"/>
+      <c r="L33" s="21" t="str"/>
+      <c r="M33" s="11" t="str"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TOOL-004</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>工具机制</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>子 agent 工具创建与执行</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>已配置 main-loop 与 subagent 标签凭据；后端运行</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>1. 主模型提案创建 subagent 型工具（含模型引用、凭据引用、预算）
+2. 审批弹窗展示预算并可修改，批准（含预算覆盖）
+3. 主循环调用该工具（同步或异步）
+4. 子 agent 用自有 Key 与模型跑独立循环
+5. 检查结果回传与 SUBAGENT_STATUS 事件（前端可折叠卡片）</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>注册成功且执行返回结果；结果超软上限时返回指针提示，read_task_result 可完整分段读取；子 agent 内仅 memory_search 可用；结果不截断</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>通过。真实模型（MiMo）子 agent 执行：异步提交返回 task_id，子 agent 用自有 Key 独立循环，await_task 取回结果「用户饮食偏清淡，忌辛辣且不饮用牛奶」；超限指针与 read_task_result 由单元/集成测试覆盖。</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="n"/>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TOOL-005</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>工具机制</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>异步并行与完成唤起</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>已注册一个异步 subagent 工具；真实模型可用</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>1. 主模型一次发起多个异步子 agent 调用
+2. 检查 pending 回喂与 task_id
+3. 同轮/跨轮 await_task 取回；或 await_task(notify=true) 注册唤起
+4. turn 结束后任务完成：观察系统驱动唤起（主 agent 主动回复）
+5. 检查通知 turn 不写 user 消息、反馈写入记忆</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>并发上限内并行执行（超出排队）；await_task 超时返回仍运行；notify 唤起后主 agent 反馈；反馈进记忆、子 agent 结果作为工具卡片展示（默认收起）</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="13" t="n"/>
+      <c r="J35" s="13" t="n"/>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>APPROVAL-001</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>审批流</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>三类审批弹窗展示与响应</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>后端运行中；对话页已连接</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>1. 依次触发工具创建、凭据授权、高影响知识三类审批
 2. 检查弹窗内容
 3. 分别批准与拒绝</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>弹窗显示对应类型标题与 payload（解释/测试摘要/授权对象）；批准与拒绝均回传后端并关闭弹窗；队列串行不堆叠</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>标题=工具创建审批 响应后关闭=true</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J27" s="13" t="str"/>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="J36" s="13" t="str"/>
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L27" s="22" t="str"/>
-      <c r="M27" s="13" t="str"/>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="L36" s="22" t="str"/>
+      <c r="M36" s="13" t="str"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>APPROVAL-002</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>审批流</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>审批超时处理</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>审批流程可触发</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>1. 触发审批但不响应
 2. 等待超时（默认 300 秒，测试可缩短）</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>超时后按拒绝处理；发起方收到 timeout 结果；无悬挂等待</t>
         </is>
       </c>
-      <c r="H28" s="13" t="str"/>
-      <c r="I28" s="13" t="str"/>
-      <c r="J28" s="13" t="str"/>
-      <c r="K28" s="13" t="str"/>
-      <c r="L28" s="22" t="str"/>
-      <c r="M28" s="13" t="str"/>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="H37" s="13" t="str"/>
+      <c r="I37" s="13" t="str"/>
+      <c r="J37" s="13" t="str"/>
+      <c r="K37" s="13" t="str"/>
+      <c r="L37" s="22" t="str"/>
+      <c r="M37" s="13" t="str"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>UI-001</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>前端交互</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>长对话虚拟滚动</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>对话页已连接</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>1. 生成大量消息（100+ 条）
 2. 上下滚动消息流
 3. 发送新消息</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>滚动流畅无明显卡顿；消息按需渲染；新消息时若处于底部则自动跟随</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>历史消息恢复=10 条；滚动容器溢出=true（100+ 消息大规模压测待补充）</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>历史消息恢复=0 条；滚动容器溢出=false（100+ 消息大规模压测待补充）</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>DEF-001</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L29" s="21" t="str"/>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>缺陷 DEF-001：历史消息恢复=10 条；滚动容器溢出=true（100+ 消息大规模压测待补充）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="L38" s="21" t="str"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>缺陷 DEF-001：历史消息恢复=0 条；滚动容器溢出=false（100+ 消息大规模压测待补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>UI-002</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>前端交互</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>悬浮球与星球过渡</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>对话页已连接</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>1. 点击右下角悬浮球
 2. 等待全屏星球
 3. 点击收起</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>星球页以过渡动画展开（相机推进）；星球渲染正常（WebGL 可用时显示 fps）；收起后回到对话页</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>WebGL=true 话题=5 收起=true</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>WebGL=true 话题=0 收起=true</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="str"/>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="str"/>
+      <c r="M39" s="11" t="str"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>UI-003</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>前端交互</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>偏好设置：封块分档控件</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>设置页可访问；后端运行</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>1. 打开设置页「偏好」卡片
+2. 依次选择 短（5 轮）/ 标准（10 轮）/ 长（15 轮），观察保存提示
+3. 选择「自定义」，输入 1-30 合法值与 0、31 非法值
+4. 刷新页面确认选中状态保持</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>分档选择即保存且后端持久化（settings 表）；刷新后选中状态保持；非法值被拒绝并提示「自定义轮数需在 1-30 之间」；页面无记忆强度滑块（已移除）</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="str"/>
+      <c r="M40" s="11" t="str"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>TOOL-006</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>工具开发工作流（创建工具的工具）</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>已配置 main-loop 凭据；后端运行</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>1. 对话中提出新工具需求，模型澄清后调用 create_tool
+2. 检查返回的工作区 id 与开发指南（需求规格必填项）
+3. 模型用 dev_write_file / dev_read_file 写定义与实现
+4. dev_run_tests 运行测试（失败则修复重跑）
+5. dev_submit_tool 提交 → 审批弹窗友好展示（用途/类型/测试摘要/预算）→ 批准
+6. 检查工具注册并可调用；工作区已清理</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>创建→实现→测试→提交→审批→注册全链路可用；技术细节以折叠工具卡片呈现（用户零暴露）；审批友好化（人话用途 + 测试摘要）；提交后双保险交叉测试；拒绝保留工作区可继续迭代</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>通过（集成验证）。主循环脚本驱动完整链路：create_tool → dev_write_file → dev_run_tests（真实沙箱）→ dev_submit_tool → 审批 → 注册 dev_add → 可调用（返回 {"sum": 5}）；工作区批准后清理；审批弹窗友好化（类型/测试摘要/预算编辑）。真实模型自主走链路由用户对话验证。</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J30" s="11" t="str"/>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L30" s="21" t="str"/>
-      <c r="M30" s="11" t="str"/>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>UI-003</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>前端交互</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>记忆强度滑块</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TOOL-007</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>工具机制</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>工具持久化与重启恢复</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>已注册一个 agent 创建的工具</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>1. 记录当前工具列表
+2. 重启后端
+3. 检查工具列表：agent 创建的工具仍可调用
+4. 新注册工具自动落库（tools 表）</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>tools 表持久化定义；重启后从库恢复注册（function/subagent 均可）；内置工具不落库；损坏定义跳过不阻塞启动</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>M12-001</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>离线任务</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>维护调度与手动触发</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>对话页已连接；已有记忆数据</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>1. 调整记忆强度滑块至 0 与 1
-2. 各发送一条消息
-3. 对比注入内容</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>滑块值影响注入预算（0 时知识域预算取下限，1 时取上限）；注入内容随强度变化可见</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>滑块值=1.00（注入预算影响需真实对话验证）</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>后端运行</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>1. 设置页开启离线维护（间隔可配）
+2. 点击「立即运行」或 POST /api/maintenance/run
+3. 检查后台执行（反驳扫描/Dreaming/工具候选）
+4. 运行中再次触发应被防重入拒绝</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>手动与周期触发可用；防重入；各任务失败隔离不影响主流程</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>通过。真实链路：反驳扫描命中（置信 0.9→0.7）+ 高影响审批请求；Dreaming 无凭据时隔离降级不崩；轨迹聚类产出 3 个工具候选；防重入由单元测试覆盖。</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="J31" s="11" t="str"/>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>e2e 自动化</t>
         </is>
       </c>
-      <c r="L31" s="21" t="str"/>
-      <c r="M31" s="11" t="str"/>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>M12-002</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>离线任务</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Dreaming 与高影响确认</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>存在 active 知识与 main-loop 凭据</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>1. 触发维护：Dreaming 子 agent 分析知识
+2. 低影响候选自动应用（correct 走 supersedes / expire revoke）
+3. 高影响候选弹窗确认后应用
+4. 反驳模式扫描：否定消息命中知识 → 置信降级（高影响弹窗提醒）</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>低影响自动落地；高影响走审批弹窗（high_impact_knowledge）；每轮候选上限 10；置信降级步长 0.2</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>M12-003</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>离线任务</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>轨迹聚类工具候选</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>存在相似用户请求 ≥3 条</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>1. 触发维护：相似用户请求聚类
+2. 簇 ≥3 生成工具候选草案
+3. 审批弹窗展示草案（名称/描述/示例/相似数）
+4. 批准 → 自动创建 dev 工作区（进入开发工作流）；拒绝丢弃</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>聚类阈值/簇大小生效；候选为需求草案；批准后衔接开发工作流；工具调用已落库（tool_calls 表）供轨迹分析</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="n"/>
+      <c r="I45" s="13" t="n"/>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>TOOL-008</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>工具机制</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>工具路由（选择性下发）</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>注册工具数 &gt; 路由上限（或构造多工具环境）</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>1. 对话中发送与某工具相关的请求
+2. 检查模型收到的工具列表（核心工具 + 相关工具子集）
+3. 模型能正常调用可见工具；核心工具（记忆/话题/异步）始终可见
+4. 工具数量超过上限时上下文不再全量膨胀
+5. 路由失败时降级全量下发</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>核心工具恒在下发列表；其余按相似度排序截断（默认上限 20）；执行仍按注册表全局查找（可见性≠可用性）；路由异常降级全量</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>通过。单元：核心工具恒包含/相似度排序/上限截断/空查询兜底/开发意图提示词加权；集成：AgentLoop 注入 tool_selector 后仅收到子集；真实对话 19/19 回归，路由后模型仍正常调用 switch_topic 等工具。</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>e2e 自动化</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>PACK-001</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>桌面打包</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>sidecar 启动与退出清理</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>已构建 Tauri 应用（sidecar 已打包）</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>1. 启动桌面应用
 2. 检查后端健康
 3. 退出应用</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>应用启动时自动拉起 Python sidecar；后端 health 通过；退出应用时 sidecar 进程被终止，无残留进程</t>
         </is>
       </c>
-      <c r="H32" s="13" t="str"/>
-      <c r="I32" s="13" t="str"/>
-      <c r="J32" s="13" t="str"/>
-      <c r="K32" s="13" t="str"/>
-      <c r="L32" s="22" t="str"/>
-      <c r="M32" s="13" t="str"/>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="H47" s="13" t="str"/>
+      <c r="I47" s="13" t="str"/>
+      <c r="J47" s="13" t="str"/>
+      <c r="K47" s="13" t="str"/>
+      <c r="L47" s="22" t="str"/>
+      <c r="M47" s="13" t="str"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>PACK-002</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>桌面打包</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>端口占用容错</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>已构建桌面应用</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>1. 手动占用 8734 端口
 2. 启动应用</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>应用不崩溃；给出明确错误提示或自动切换端口；可恢复</t>
         </is>
       </c>
-      <c r="H33" s="13" t="str"/>
-      <c r="I33" s="13" t="str"/>
-      <c r="J33" s="13" t="str"/>
-      <c r="K33" s="13" t="str"/>
-      <c r="L33" s="22" t="str"/>
-      <c r="M33" s="13" t="str"/>
+      <c r="H48" s="13" t="str"/>
+      <c r="I48" s="13" t="str"/>
+      <c r="J48" s="13" t="str"/>
+      <c r="K48" s="13" t="str"/>
+      <c r="L48" s="22" t="str"/>
+      <c r="M48" s="13" t="str"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M33"/>
+  <autoFilter ref="A3:M48"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,阻塞,跳过"</formula1>
     </dataValidation>
-    <dataValidation sqref="L4:L33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="无效日期" error="请输入有效日期（yyyy-mm-dd）" type="date" errorStyle="stop">
+    <dataValidation sqref="L4:L48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="无效日期" error="请输入有效日期（yyyy-mm-dd）" type="date" errorStyle="stop">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
